--- a/assets/constructions/examples/ctd_tko_back_boring.xlsx
+++ b/assets/constructions/examples/ctd_tko_back_boring.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ctd" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ctd" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH6"/>
+  <dimension ref="A1:AM6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -599,11 +599,36 @@
           <t>releasepack</t>
         </is>
       </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>lcs</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>pricecurrency</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue_rub</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>V14BBRVBX</t>
+          <t>V08BBRVBX</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -618,7 +643,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>V14</t>
+          <t>V08</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,22 +658,22 @@
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
-        <v>13.8</v>
+        <v>7.8</v>
       </c>
       <c r="I2" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="J2" t="n">
-        <v>8.699999999999999</v>
+        <v>4.65</v>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="n">
-        <v>5.6</v>
+        <v>3.8</v>
       </c>
       <c r="O2" t="n">
-        <v>3.5</v>
+        <v>1.2</v>
       </c>
       <c r="P2" t="n">
         <v>0.2</v>
@@ -666,7 +691,7 @@
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="inlineStr">
         <is>
-          <t>VARGUS_V14</t>
+          <t>VARGUS_V08</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
@@ -709,13 +734,24 @@
       <c r="AH2" t="inlineStr">
         <is>
           <t>2019 / Groovex Catalog</t>
+        </is>
+      </c>
+      <c r="AI2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>PMKNSH</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>VE11020BB RVTX</t>
+          <t>V14BBR VTX</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -728,8 +764,16 @@
           <t>Mini-V</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>V14</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>VARGUS</t>
+        </is>
+      </c>
       <c r="F3" t="inlineStr">
         <is>
           <t>PMKNSH</t>
@@ -737,22 +781,22 @@
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
-        <v>11</v>
+        <v>13.8</v>
       </c>
       <c r="I3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J3" t="n">
-        <v>6.7</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="n">
-        <v>5.85</v>
-      </c>
-      <c r="N3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="n">
+        <v>5.6</v>
+      </c>
       <c r="O3" t="n">
-        <v>2.2</v>
+        <v>3.5</v>
       </c>
       <c r="P3" t="n">
         <v>0.2</v>
@@ -762,19 +806,15 @@
           <t>R</t>
         </is>
       </c>
-      <c r="R3" t="n">
-        <v>-6.7</v>
-      </c>
+      <c r="R3" t="inlineStr"/>
       <c r="S3" t="n">
-        <v>96.7</v>
-      </c>
-      <c r="T3" t="n">
-        <v>23.3</v>
-      </c>
+        <v>59.5</v>
+      </c>
+      <c r="T3" t="inlineStr"/>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="inlineStr">
         <is>
-          <t>VARGUS_V11</t>
+          <t>VARGUS_V14</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -816,14 +856,33 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>2021/Groovex Vargus</t>
+          <t>2019 / Groovex Catalog</t>
+        </is>
+      </c>
+      <c r="AI3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>33.33</v>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AL3" t="n">
+        <v>3064.15</v>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>PMKNSH</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>V08BBRVBX</t>
+          <t>VE08020BB LVTX</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -836,16 +895,8 @@
           <t>Mini-V</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>V08</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>VARGUS</t>
-        </is>
-      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
           <t>PMKNSH</t>
@@ -863,10 +914,10 @@
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="n">
-        <v>3.8</v>
-      </c>
+      <c r="M4" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="O4" t="n">
         <v>1.2</v>
       </c>
@@ -875,14 +926,18 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr"/>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="R4" t="n">
+        <v>-4.7</v>
+      </c>
       <c r="S4" t="n">
-        <v>59.5</v>
-      </c>
-      <c r="T4" t="inlineStr"/>
+        <v>94.7</v>
+      </c>
+      <c r="T4" t="n">
+        <v>25.4</v>
+      </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="inlineStr">
         <is>
@@ -901,12 +956,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>VBX</t>
+          <t>VTX</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>TiCN</t>
+          <t>TiAlN</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr"/>
@@ -928,14 +983,33 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>2019 / Groovex Catalog</t>
+          <t>2021/Groovex Vargus</t>
+        </is>
+      </c>
+      <c r="AI4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>25.48</v>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AL4" t="n">
+        <v>2342.47</v>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>PMKNSH</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>VE11020BB LVTX</t>
+          <t>V14BBRVBX</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -948,8 +1022,16 @@
           <t>Mini-V</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>V14</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>VARGUS</t>
+        </is>
+      </c>
       <c r="F5" t="inlineStr">
         <is>
           <t>PMKNSH</t>
@@ -957,44 +1039,40 @@
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
-        <v>11</v>
+        <v>13.8</v>
       </c>
       <c r="I5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J5" t="n">
-        <v>6.7</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="n">
-        <v>5.85</v>
-      </c>
-      <c r="N5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="n">
+        <v>5.6</v>
+      </c>
       <c r="O5" t="n">
-        <v>2.2</v>
+        <v>3.5</v>
       </c>
       <c r="P5" t="n">
         <v>0.2</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="R5" t="n">
-        <v>-6.7</v>
-      </c>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
-        <v>96.7</v>
-      </c>
-      <c r="T5" t="n">
-        <v>23.3</v>
-      </c>
+        <v>59.5</v>
+      </c>
+      <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="inlineStr">
         <is>
-          <t>VARGUS_V11</t>
+          <t>VARGUS_V14</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1009,12 +1087,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>VTX</t>
+          <t>VBX</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>TiAlN</t>
+          <t>TiCN</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr"/>
@@ -1036,14 +1114,33 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>2021/Groovex Vargus</t>
+          <t>2019 / Groovex Catalog</t>
+        </is>
+      </c>
+      <c r="AI5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>33.33</v>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AL5" t="n">
+        <v>3064.15</v>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>PMKNSH</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>VE08020BB RVTX</t>
+          <t>VE11020BB RVTX</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1065,22 +1162,22 @@
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
-        <v>7.8</v>
+        <v>11</v>
       </c>
       <c r="I6" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J6" t="n">
-        <v>4.65</v>
+        <v>6.7</v>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
-        <v>4.6</v>
+        <v>5.85</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="n">
-        <v>1.2</v>
+        <v>2.2</v>
       </c>
       <c r="P6" t="n">
         <v>0.2</v>
@@ -1091,18 +1188,18 @@
         </is>
       </c>
       <c r="R6" t="n">
-        <v>-4.7</v>
+        <v>-6.7</v>
       </c>
       <c r="S6" t="n">
-        <v>94.7</v>
+        <v>96.7</v>
       </c>
       <c r="T6" t="n">
-        <v>25.4</v>
+        <v>23.3</v>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="inlineStr">
         <is>
-          <t>VARGUS_V08</t>
+          <t>VARGUS_V11</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1145,6 +1242,25 @@
       <c r="AH6" t="inlineStr">
         <is>
           <t>2021/Groovex Vargus</t>
+        </is>
+      </c>
+      <c r="AI6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>25.48</v>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AL6" t="n">
+        <v>2342.47</v>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>PMKNSH</t>
         </is>
       </c>
     </row>
